--- a/artfynd/A 28856-2021 artfynd.xlsx
+++ b/artfynd/A 28856-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 28856-2021 artfynd.xlsx
+++ b/artfynd/A 28856-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4877,10 +4877,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>116935557</v>
+        <v>116935553</v>
       </c>
       <c r="B37" t="n">
-        <v>97777</v>
+        <v>79550</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4889,25 +4889,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4917,10 +4917,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>622947</v>
+        <v>622981</v>
       </c>
       <c r="R37" t="n">
-        <v>7213698</v>
+        <v>7213744</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4984,10 +4984,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>116935575</v>
+        <v>116935576</v>
       </c>
       <c r="B38" t="n">
-        <v>90735</v>
+        <v>90894</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4996,25 +4996,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5088,546 +5088,6 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>116935553</v>
-      </c>
-      <c r="B39" t="n">
-        <v>79550</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>6462</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Stuplav</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Barsele, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q39" t="n">
-        <v>622981</v>
-      </c>
-      <c r="R39" t="n">
-        <v>7213744</v>
-      </c>
-      <c r="S39" t="n">
-        <v>10</v>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>Storuman</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>Stensele</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>2018-08-02</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>2018-08-02</t>
-        </is>
-      </c>
-      <c r="AD39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AS39" t="inlineStr">
-        <is>
-          <t>Jörgen Olsson</t>
-        </is>
-      </c>
-      <c r="AT39" t="inlineStr"/>
-      <c r="AW39" t="inlineStr">
-        <is>
-          <t>Elin Lindmark</t>
-        </is>
-      </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>Via Elin Lindmark</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>116935561</v>
-      </c>
-      <c r="B40" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Barsele, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q40" t="n">
-        <v>622894</v>
-      </c>
-      <c r="R40" t="n">
-        <v>7213672</v>
-      </c>
-      <c r="S40" t="n">
-        <v>10</v>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>Storuman</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>Stensele</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>2018-08-02</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>2018-08-02</t>
-        </is>
-      </c>
-      <c r="AD40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AS40" t="inlineStr">
-        <is>
-          <t>Jörgen Olsson</t>
-        </is>
-      </c>
-      <c r="AT40" t="inlineStr"/>
-      <c r="AW40" t="inlineStr">
-        <is>
-          <t>Elin Lindmark</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>Via Elin Lindmark</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>116935576</v>
-      </c>
-      <c r="B41" t="n">
-        <v>90894</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Phlebia centrifuga</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Barsele, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q41" t="n">
-        <v>623023</v>
-      </c>
-      <c r="R41" t="n">
-        <v>7213665</v>
-      </c>
-      <c r="S41" t="n">
-        <v>10</v>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Storuman</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>Stensele</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>2018-06-15</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>2018-06-15</t>
-        </is>
-      </c>
-      <c r="AD41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AS41" t="inlineStr">
-        <is>
-          <t>Jörgen Olsson</t>
-        </is>
-      </c>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr">
-        <is>
-          <t>Elin Lindmark</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>Via Elin Lindmark</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>116935562</v>
-      </c>
-      <c r="B42" t="n">
-        <v>79521</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Barsele, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q42" t="n">
-        <v>622894</v>
-      </c>
-      <c r="R42" t="n">
-        <v>7213672</v>
-      </c>
-      <c r="S42" t="n">
-        <v>10</v>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Storuman</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>Stensele</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>2018-08-02</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>2018-08-02</t>
-        </is>
-      </c>
-      <c r="AD42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AS42" t="inlineStr">
-        <is>
-          <t>Jörgen Olsson</t>
-        </is>
-      </c>
-      <c r="AT42" t="inlineStr"/>
-      <c r="AW42" t="inlineStr">
-        <is>
-          <t>Elin Lindmark</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>Via Elin Lindmark</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>116935577</v>
-      </c>
-      <c r="B43" t="n">
-        <v>90735</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>658</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Rosenticka</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Rhodofomes roseus</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Barsele, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q43" t="n">
-        <v>622984</v>
-      </c>
-      <c r="R43" t="n">
-        <v>7213678</v>
-      </c>
-      <c r="S43" t="n">
-        <v>10</v>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>Storuman</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>Stensele</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>2018-06-15</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>2018-06-15</t>
-        </is>
-      </c>
-      <c r="AD43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AS43" t="inlineStr">
-        <is>
-          <t>Jörgen Olsson</t>
-        </is>
-      </c>
-      <c r="AT43" t="inlineStr"/>
-      <c r="AW43" t="inlineStr">
-        <is>
-          <t>Elin Lindmark</t>
-        </is>
-      </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>Via Elin Lindmark</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
